--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_334_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_334_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
         <v>10</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,10 +1335,10 @@
         <v>23</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1531,7 +1531,7 @@
         <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1727,10 +1727,10 @@
         <v>27</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2122,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2315,16 +2315,16 @@
         <v>5</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
         <v>1</v>
@@ -3827,16 +3827,16 @@
         <v>97</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
         <v>23</v>
@@ -4295,7 +4295,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
         <v>27</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -5272,16 +5272,16 @@
         <v>22</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
         <v>6</v>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -5863,13 +5863,13 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X43" t="n">
         <v>6</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>143</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X48" t="n">
         <v>32</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_334_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_334_EL.xlsx
@@ -674,10 +674,10 @@
         <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="O2" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="P2" t="n">
         <v>7</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>95.83</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="O3" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>91.43</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -1739,10 +1739,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -1935,14 +1935,14 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA20" t="n">
@@ -2327,14 +2327,14 @@
         <v>1</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA22" t="n">
@@ -3307,14 +3307,14 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3839,14 +3839,14 @@
         <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="Y30" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -5088,10 +5088,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
@@ -5284,14 +5284,14 @@
         <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5480,14 +5480,14 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y41" t="n">
         <v>4</v>
       </c>
-      <c r="Y41" t="n">
-        <v>5</v>
-      </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5676,14 +5676,14 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA42" t="n">
@@ -5872,10 +5872,10 @@
         <v>2</v>
       </c>
       <c r="X43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
@@ -6264,14 +6264,14 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA45" t="n">
@@ -6460,10 +6460,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y46" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
@@ -6796,14 +6796,14 @@
         <v>3</v>
       </c>
       <c r="X48" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="Y48" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA48" t="n">
